--- a/UPMPackages/com.solotopia.nova.framework.sdk.firebase/Nova/Tracks/Tracks.xlsx
+++ b/UPMPackages/com.solotopia.nova.framework.sdk.firebase/Nova/Tracks/Tracks.xlsx
@@ -217,50 +217,64 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="134"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体-简"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -275,8 +289,20 @@
         <fgColor rgb="FFEAF4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF4EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -336,62 +362,208 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C7D6"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C7D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C7D6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C7D6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C7D6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7C7D6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -679,141 +851,192 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="1" width="35" style="1" customWidth="1"/>
-    <col min="2" max="2" width="31" style="1" customWidth="1"/>
-    <col min="3" max="3" width="55" style="1" customWidth="1"/>
-    <col min="4" max="4" width="40" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="7" width="55" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="55" style="1" customWidth="1"/>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36" customWidth="1" style="1" min="3" max="3"/>
+    <col width="40" customWidth="1" style="1" min="4" max="4"/>
+    <col width="14" customWidth="1" style="1" min="5" max="5"/>
+    <col width="58" customWidth="1" style="1" min="6" max="6"/>
+    <col width="32" customWidth="1" style="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="1" min="8" max="8"/>
+    <col width="48" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="3" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
+    <row r="1" ht="17" customHeight="1" s="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>事件名</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>事件中文名</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>事件说明</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>属性名</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>属性类型</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>属性说明</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>上报时机</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:9" s="5" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="7"/>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>nova_firebase_fcm_click</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>通知消息点击</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>点击通知消息打开app时上报一次</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>nova_firebase_fcm_message_id</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>Firebase 的消息ID</t>
+        </is>
+      </c>
+      <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>点击通知消息时上报</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
+        <is>
+          <t>tga</t>
+        </is>
+      </c>
+      <c r="I2" s="16" t="n"/>
     </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="9"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
+    <row r="3">
+      <c r="A3" s="17" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>nova_firebase_push_task_id</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>GM 后台创建的任务 ID</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="n"/>
+      <c r="I3" s="16" t="n"/>
     </row>
-    <row r="4" spans="1:9" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+    <row r="4">
+      <c r="A4" s="17" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>nova_firebase_push_task_key</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">对应协议上传的 task_key </t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="n"/>
+      <c r="I4" s="16" t="n"/>
     </row>
-    <row r="5" spans="1:9" s="5" customFormat="1" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+    <row r="5">
+      <c r="A5" s="18" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>nova_firebase_template_id</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>GM 后台的消息模板ID</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="n"/>
+      <c r="I5" s="16" t="n"/>
     </row>
-    <row r="6" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="6">
+  <autoFilter ref="A1:I5"/>
+  <mergeCells count="3">
     <mergeCell ref="A2:A5"/>
+    <mergeCell ref="C2:C5"/>
     <mergeCell ref="B2:B5"/>
-    <mergeCell ref="C2:C5"/>
-    <mergeCell ref="G2:G5"/>
-    <mergeCell ref="H2:H5"/>
-    <mergeCell ref="I2:I5"/>
   </mergeCells>
-  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>